--- a/data/templates/prediction_output.xlsx
+++ b/data/templates/prediction_output.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="1" r:id="R5ed31d1e8ce34b36"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prediction_Output" sheetId="2" r:id="R4ca77bd27ad04094"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="1" r:id="R77c206f42ec64e4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Prediction_Output" sheetId="2" r:id="R711b9b2d5faf47bb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -418,7 +418,7 @@
         <x:v>Purpose</x:v>
       </x:c>
       <x:c r="B4" s="21" t="str">
-        <x:v>Machine-generated API/download result and the tabular input for the dashboard.</x:v>
+        <x:v>Machine-generated Excel result workbook and the tabular input for the dashboard.</x:v>
       </x:c>
       <x:c r="C4" s="21"/>
       <x:c r="D4" s="21"/>
@@ -428,7 +428,7 @@
         <x:v>One row means</x:v>
       </x:c>
       <x:c r="B5" s="21" t="str">
-        <x:v>One processed row from Batch_Input.</x:v>
+        <x:v>One processed row from the Batch_Input worksheet.</x:v>
       </x:c>
       <x:c r="C5" s="21"/>
       <x:c r="D5" s="21"/>
@@ -478,7 +478,7 @@
         <x:v>Editing rule</x:v>
       </x:c>
       <x:c r="B10" s="21" t="str">
-        <x:v>Do not fill this sheet manually. The pipeline/API generates it from Batch_Input.</x:v>
+        <x:v>Do not fill this sheet manually. The pipeline generates it from the batch_input.xlsx workbook.</x:v>
       </x:c>
       <x:c r="C10" s="21"/>
       <x:c r="D10" s="21"/>
@@ -488,7 +488,7 @@
         <x:v>Git / sharing</x:v>
       </x:c>
       <x:c r="B11" s="21" t="str">
-        <x:v>The empty schema template can be stored in Git. Generated prediction files should follow the project’s approved data-sharing rules.</x:v>
+        <x:v>The empty Excel template can be stored in Git. Generated prediction workbooks must follow approved sharing rules.</x:v>
       </x:c>
       <x:c r="C11" s="21"/>
       <x:c r="D11" s="21"/>
@@ -854,7 +854,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R113cb3adf8b1451e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9f79878c1a8f4a95"/>
   </x:tableParts>
 </x:worksheet>
 </file>